--- a/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_run_3/epoch_80/per_file_predictions_epoch_80.xlsx
+++ b/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_run_3/epoch_80/per_file_predictions_epoch_80.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="519">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="518">
   <si>
     <t>Filename</t>
   </si>
@@ -808,769 +808,766 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0.9603,0.0014,0.0183,0.0040</t>
-  </si>
-  <si>
-    <t>0.9500,0.0010,0.0056,0.0217</t>
-  </si>
-  <si>
-    <t>0.6288,0.0853,0.0496,0.0911</t>
-  </si>
-  <si>
-    <t>0.9854,0.0009,0.0013,0.0041</t>
-  </si>
-  <si>
-    <t>0.9619,0.0029,0.0018,0.0177</t>
-  </si>
-  <si>
-    <t>0.9392,0.0029,0.0008,0.0377</t>
-  </si>
-  <si>
-    <t>0.9457,0.0056,0.0068,0.0250</t>
-  </si>
-  <si>
-    <t>0.9128,0.0097,0.0150,0.0410</t>
-  </si>
-  <si>
-    <t>0.9481,0.0059,0.0184,0.0088</t>
-  </si>
-  <si>
-    <t>0.9201,0.0038,0.0045,0.0552</t>
-  </si>
-  <si>
-    <t>0.9374,0.0056,0.0073,0.0200</t>
-  </si>
-  <si>
-    <t>0.9712,0.0035,0.0026,0.0068</t>
-  </si>
-  <si>
-    <t>0.9814,0.0007,0.0183,0.0001</t>
-  </si>
-  <si>
-    <t>0.6745,0.0097,0.3815,0.0069</t>
-  </si>
-  <si>
-    <t>0.9797,0.0008,0.0143,0.0003</t>
-  </si>
-  <si>
-    <t>0.9000,0.0018,0.1686,0.0008</t>
-  </si>
-  <si>
-    <t>0.9545,0.0011,0.0611,0.0003</t>
-  </si>
-  <si>
-    <t>0.9247,0.0538,0.0082,0.0002</t>
-  </si>
-  <si>
-    <t>0.9631,0.0071,0.0138,0.0009</t>
-  </si>
-  <si>
-    <t>0.9804,0.0029,0.0030,0.0012</t>
-  </si>
-  <si>
-    <t>0.6070,0.3283,0.0544,0.0012</t>
-  </si>
-  <si>
-    <t>0.9385,0.0213,0.0179,0.0009</t>
-  </si>
-  <si>
-    <t>0.9268,0.0015,0.0927,0.0009</t>
-  </si>
-  <si>
-    <t>0.9821,0.0002,0.0252,0.0001</t>
-  </si>
-  <si>
-    <t>0.0853,0.0151,0.9691,0.0003</t>
-  </si>
-  <si>
-    <t>0.9295,0.0010,0.0829,0.0011</t>
-  </si>
-  <si>
-    <t>0.9658,0.0007,0.0379,0.0005</t>
-  </si>
-  <si>
-    <t>0.6607,0.0039,0.5210,0.0019</t>
-  </si>
-  <si>
-    <t>0.4316,0.0106,0.7013,0.0009</t>
-  </si>
-  <si>
-    <t>0.9349,0.0175,0.0291,0.0031</t>
-  </si>
-  <si>
-    <t>0.9665,0.0035,0.0074,0.0056</t>
-  </si>
-  <si>
-    <t>0.0086,0.0358,0.9911,0.0026</t>
-  </si>
-  <si>
-    <t>0.9291,0.0094,0.0502,0.0012</t>
-  </si>
-  <si>
-    <t>0.9903,0.0008,0.0017,0.0013</t>
-  </si>
-  <si>
-    <t>0.9629,0.0014,0.0115,0.0054</t>
-  </si>
-  <si>
-    <t>0.9653,0.0048,0.0108,0.0026</t>
-  </si>
-  <si>
-    <t>0.9349,0.0149,0.0296,0.0061</t>
-  </si>
-  <si>
-    <t>0.1190,0.0272,0.9400,0.0014</t>
-  </si>
-  <si>
-    <t>0.7601,0.0012,0.4659,0.0002</t>
-  </si>
-  <si>
-    <t>0.9688,0.0010,0.0397,0.0002</t>
-  </si>
-  <si>
-    <t>0.8558,0.0014,0.1674,0.0025</t>
-  </si>
-  <si>
-    <t>0.6306,0.0238,0.5129,0.0005</t>
-  </si>
-  <si>
-    <t>0.2581,0.6039,0.0937,0.0009</t>
-  </si>
-  <si>
-    <t>0.8158,0.0020,0.3446,0.0005</t>
-  </si>
-  <si>
-    <t>0.9068,0.0274,0.0398,0.0061</t>
-  </si>
-  <si>
-    <t>0.9756,0.0035,0.0057,0.0014</t>
-  </si>
-  <si>
-    <t>0.9627,0.0085,0.0092,0.0008</t>
-  </si>
-  <si>
-    <t>0.9434,0.0338,0.0043,0.0007</t>
-  </si>
-  <si>
-    <t>0.0392,0.0283,0.9740,0.0007</t>
-  </si>
-  <si>
-    <t>0.0055,0.0048,0.9965,0.0001</t>
-  </si>
-  <si>
-    <t>0.2691,0.0080,0.8208,0.0036</t>
-  </si>
-  <si>
-    <t>0.4537,0.0006,0.7445,0.0009</t>
-  </si>
-  <si>
-    <t>0.0621,0.0160,0.9677,0.0014</t>
-  </si>
-  <si>
-    <t>0.1739,0.0103,0.8997,0.0011</t>
-  </si>
-  <si>
-    <t>0.9495,0.0046,0.0034,0.0239</t>
-  </si>
-  <si>
-    <t>0.9755,0.0010,0.0007,0.0148</t>
-  </si>
-  <si>
-    <t>0.8747,0.0242,0.0196,0.0237</t>
-  </si>
-  <si>
-    <t>0.0917,0.0280,0.8515,0.1022</t>
-  </si>
-  <si>
-    <t>0.8847,0.0018,0.0020,0.1737</t>
-  </si>
-  <si>
-    <t>0.9547,0.0022,0.0019,0.0383</t>
-  </si>
-  <si>
-    <t>0.9585,0.0038,0.0045,0.0114</t>
-  </si>
-  <si>
-    <t>0.0252,0.5607,0.9432,0.0011</t>
-  </si>
-  <si>
-    <t>0.3869,0.0029,0.8538,0.0002</t>
-  </si>
-  <si>
-    <t>0.0581,0.0223,0.9669,0.0007</t>
-  </si>
-  <si>
-    <t>0.0058,0.2726,0.9926,0.0002</t>
-  </si>
-  <si>
-    <t>0.3898,0.0117,0.7985,0.0015</t>
-  </si>
-  <si>
-    <t>0.7827,0.2716,0.0093,0.0003</t>
-  </si>
-  <si>
-    <t>0.0939,0.9561,0.0114,0.0002</t>
-  </si>
-  <si>
-    <t>0.9610,0.0017,0.0277,0.0025</t>
-  </si>
-  <si>
-    <t>0.9526,0.0099,0.0212,0.0014</t>
-  </si>
-  <si>
-    <t>0.0033,0.0316,0.9855,0.0009</t>
-  </si>
-  <si>
-    <t>0.2345,0.2100,0.7440,0.0015</t>
-  </si>
-  <si>
-    <t>0.5743,0.0552,0.4885,0.0012</t>
-  </si>
-  <si>
-    <t>0.2827,0.5226,0.3573,0.0039</t>
-  </si>
-  <si>
-    <t>0.0561,0.5648,0.7250,0.0006</t>
-  </si>
-  <si>
-    <t>0.7394,0.0025,0.0385,0.1258</t>
-  </si>
-  <si>
-    <t>0.9611,0.0001,0.0002,0.0540</t>
-  </si>
-  <si>
-    <t>0.5566,0.0000,0.0002,0.6960</t>
-  </si>
-  <si>
-    <t>0.8630,0.0002,0.0011,0.1910</t>
-  </si>
-  <si>
-    <t>0.9748,0.0000,0.0002,0.0237</t>
-  </si>
-  <si>
-    <t>0.8626,0.0007,0.0022,0.1809</t>
-  </si>
-  <si>
-    <t>0.0332,0.2692,0.9738,0.0003</t>
-  </si>
-  <si>
-    <t>0.3209,0.0097,0.8910,0.0002</t>
-  </si>
-  <si>
-    <t>0.1130,0.0102,0.9516,0.0003</t>
-  </si>
-  <si>
-    <t>0.0208,0.0345,0.9880,0.0002</t>
-  </si>
-  <si>
-    <t>0.2619,0.2218,0.7094,0.0017</t>
-  </si>
-  <si>
-    <t>0.4645,0.0218,0.7625,0.0017</t>
-  </si>
-  <si>
-    <t>0.9371,0.0068,0.0028,0.0225</t>
-  </si>
-  <si>
-    <t>0.9835,0.0009,0.0015,0.0073</t>
-  </si>
-  <si>
-    <t>0.9529,0.0134,0.0035,0.0038</t>
-  </si>
-  <si>
-    <t>0.9614,0.0019,0.0023,0.0165</t>
-  </si>
-  <si>
-    <t>0.9841,0.0024,0.0018,0.0045</t>
-  </si>
-  <si>
-    <t>0.9143,0.0010,0.0010,0.1324</t>
-  </si>
-  <si>
-    <t>0.9623,0.0013,0.0013,0.0285</t>
-  </si>
-  <si>
-    <t>0.9760,0.0039,0.0032,0.0033</t>
-  </si>
-  <si>
-    <t>0.9254,0.0009,0.0009,0.1378</t>
-  </si>
-  <si>
-    <t>0.9207,0.0012,0.0023,0.0931</t>
-  </si>
-  <si>
-    <t>0.9095,0.0027,0.0005,0.0567</t>
-  </si>
-  <si>
-    <t>0.9505,0.0030,0.0022,0.0274</t>
-  </si>
-  <si>
-    <t>0.9484,0.0009,0.0010,0.0599</t>
-  </si>
-  <si>
-    <t>0.9712,0.0005,0.0010,0.0267</t>
-  </si>
-  <si>
-    <t>0.7666,0.0019,0.0011,0.3508</t>
-  </si>
-  <si>
-    <t>0.9460,0.0015,0.0011,0.0540</t>
-  </si>
-  <si>
-    <t>0.0792,0.0041,0.9754,0.0015</t>
-  </si>
-  <si>
-    <t>0.4619,0.0269,0.6601,0.0012</t>
-  </si>
-  <si>
-    <t>0.9927,0.0001,0.0043,0.0002</t>
-  </si>
-  <si>
-    <t>0.9549,0.0002,0.0406,0.0005</t>
-  </si>
-  <si>
-    <t>0.7659,0.1000,0.0288,0.0172</t>
-  </si>
-  <si>
-    <t>0.8730,0.0414,0.0212,0.0064</t>
-  </si>
-  <si>
-    <t>0.8489,0.0538,0.0136,0.0064</t>
-  </si>
-  <si>
-    <t>0.9152,0.0391,0.0090,0.0032</t>
-  </si>
-  <si>
-    <t>0.5343,0.4708,0.0262,0.0027</t>
-  </si>
-  <si>
-    <t>0.2499,0.7140,0.1115,0.0089</t>
-  </si>
-  <si>
-    <t>0.9630,0.0034,0.0052,0.0073</t>
-  </si>
-  <si>
-    <t>0.9050,0.0062,0.0492,0.0109</t>
-  </si>
-  <si>
-    <t>0.6872,0.0101,0.4359,0.0037</t>
-  </si>
-  <si>
-    <t>0.9737,0.0010,0.0143,0.0015</t>
-  </si>
-  <si>
-    <t>0.9810,0.0021,0.0067,0.0008</t>
-  </si>
-  <si>
-    <t>0.8374,0.0065,0.0609,0.0356</t>
-  </si>
-  <si>
-    <t>0.9801,0.0042,0.0045,0.0001</t>
-  </si>
-  <si>
-    <t>0.9865,0.0076,0.0009,0.0001</t>
-  </si>
-  <si>
-    <t>0.9334,0.0073,0.0415,0.0008</t>
-  </si>
-  <si>
-    <t>0.6299,0.3150,0.0540,0.0028</t>
-  </si>
-  <si>
-    <t>0.9424,0.0153,0.0190,0.0018</t>
-  </si>
-  <si>
-    <t>0.8440,0.0348,0.0945,0.0073</t>
-  </si>
-  <si>
-    <t>0.8722,0.0197,0.0513,0.0141</t>
-  </si>
-  <si>
-    <t>0.9539,0.0073,0.0173,0.0043</t>
-  </si>
-  <si>
-    <t>0.9684,0.0012,0.0022,0.0185</t>
-  </si>
-  <si>
-    <t>0.9079,0.0144,0.0083,0.0281</t>
-  </si>
-  <si>
-    <t>0.9767,0.0013,0.0018,0.0055</t>
-  </si>
-  <si>
-    <t>0.9653,0.0014,0.0052,0.0153</t>
-  </si>
-  <si>
-    <t>0.9871,0.0008,0.0049,0.0010</t>
-  </si>
-  <si>
-    <t>0.9005,0.0037,0.0147,0.0358</t>
-  </si>
-  <si>
-    <t>0.9396,0.0006,0.0016,0.0399</t>
-  </si>
-  <si>
-    <t>0.0800,0.0112,0.9649,0.0002</t>
-  </si>
-  <si>
-    <t>0.7235,0.0188,0.4041,0.0003</t>
-  </si>
-  <si>
-    <t>0.2573,0.0027,0.8864,0.0003</t>
-  </si>
-  <si>
-    <t>0.4614,0.0063,0.7252,0.0005</t>
-  </si>
-  <si>
-    <t>0.9941,0.0002,0.0023,0.0001</t>
-  </si>
-  <si>
-    <t>0.9812,0.0006,0.0048,0.0014</t>
-  </si>
-  <si>
-    <t>0.8569,0.0031,0.1540,0.0032</t>
-  </si>
-  <si>
-    <t>0.9660,0.0016,0.0221,0.0011</t>
-  </si>
-  <si>
-    <t>0.9866,0.0001,0.0013,0.0032</t>
-  </si>
-  <si>
-    <t>0.3540,0.0003,0.0030,0.7943</t>
-  </si>
-  <si>
-    <t>0.2911,0.0022,0.0103,0.7908</t>
-  </si>
-  <si>
-    <t>0.9066,0.0002,0.0010,0.1104</t>
-  </si>
-  <si>
-    <t>0.3929,0.0284,0.7646,0.0002</t>
-  </si>
-  <si>
-    <t>0.9799,0.0013,0.0036,0.0051</t>
-  </si>
-  <si>
-    <t>0.8960,0.0337,0.0092,0.0078</t>
-  </si>
-  <si>
-    <t>0.9782,0.0007,0.0010,0.0097</t>
-  </si>
-  <si>
-    <t>0.8025,0.0240,0.0245,0.0720</t>
-  </si>
-  <si>
-    <t>0.9119,0.0018,0.0016,0.1072</t>
-  </si>
-  <si>
-    <t>0.9607,0.0007,0.0030,0.0213</t>
-  </si>
-  <si>
-    <t>0.9238,0.0040,0.0034,0.0479</t>
-  </si>
-  <si>
-    <t>0.1445,0.0768,0.8897,0.0179</t>
-  </si>
-  <si>
-    <t>0.9563,0.0020,0.0058,0.0154</t>
-  </si>
-  <si>
-    <t>0.9521,0.0012,0.0023,0.0206</t>
-  </si>
-  <si>
-    <t>0.9252,0.0039,0.0396,0.0038</t>
-  </si>
-  <si>
-    <t>0.9968,0.0001,0.0007,0.0001</t>
-  </si>
-  <si>
-    <t>0.9861,0.0006,0.0025,0.0019</t>
-  </si>
-  <si>
-    <t>0.9368,0.0163,0.0171,0.0012</t>
-  </si>
-  <si>
-    <t>0.9729,0.0048,0.0108,0.0005</t>
-  </si>
-  <si>
-    <t>0.9920,0.0004,0.0029,0.0003</t>
-  </si>
-  <si>
-    <t>0.9797,0.0017,0.0017,0.0042</t>
-  </si>
-  <si>
-    <t>0.9661,0.0006,0.0008,0.0400</t>
-  </si>
-  <si>
-    <t>0.9232,0.0030,0.0045,0.0399</t>
-  </si>
-  <si>
-    <t>0.9028,0.0016,0.0032,0.0827</t>
-  </si>
-  <si>
-    <t>0.6695,0.0123,0.0363,0.2229</t>
-  </si>
-  <si>
-    <t>0.9545,0.0030,0.0013,0.0239</t>
-  </si>
-  <si>
-    <t>0.8221,0.0031,0.0010,0.1774</t>
-  </si>
-  <si>
-    <t>0.9798,0.0006,0.0005,0.0139</t>
-  </si>
-  <si>
-    <t>0.9056,0.0191,0.0367,0.0130</t>
-  </si>
-  <si>
-    <t>0.9458,0.0068,0.0135,0.0046</t>
-  </si>
-  <si>
-    <t>0.9453,0.0038,0.0198,0.0050</t>
-  </si>
-  <si>
-    <t>0.9711,0.0022,0.0040,0.0133</t>
-  </si>
-  <si>
-    <t>0.9671,0.0035,0.0037,0.0076</t>
-  </si>
-  <si>
-    <t>0.9873,0.0005,0.0010,0.0026</t>
-  </si>
-  <si>
-    <t>0.9042,0.0030,0.0038,0.0685</t>
-  </si>
-  <si>
-    <t>0.9545,0.0057,0.0038,0.0092</t>
-  </si>
-  <si>
-    <t>0.1998,0.1111,0.8334,0.0055</t>
-  </si>
-  <si>
-    <t>0.8128,0.0412,0.0568,0.0301</t>
-  </si>
-  <si>
-    <t>0.0118,0.0356,0.9818,0.0004</t>
-  </si>
-  <si>
-    <t>0.2624,0.0277,0.8552,0.0017</t>
-  </si>
-  <si>
-    <t>0.9501,0.0025,0.0641,0.0007</t>
-  </si>
-  <si>
-    <t>0.5078,0.0706,0.5553,0.0020</t>
-  </si>
-  <si>
-    <t>0.5653,0.0047,0.6792,0.0007</t>
-  </si>
-  <si>
-    <t>0.0122,0.0047,0.9903,0.0011</t>
-  </si>
-  <si>
-    <t>0.3024,0.0011,0.8886,0.0001</t>
-  </si>
-  <si>
-    <t>0.8917,0.0009,0.0887,0.0048</t>
-  </si>
-  <si>
-    <t>0.9836,0.0005,0.0153,0.0002</t>
-  </si>
-  <si>
-    <t>0.8899,0.0040,0.1393,0.0019</t>
-  </si>
-  <si>
-    <t>0.8435,0.0192,0.1425,0.0027</t>
-  </si>
-  <si>
-    <t>0.4580,0.1591,0.4573,0.0079</t>
-  </si>
-  <si>
-    <t>0.9309,0.0036,0.0533,0.0019</t>
-  </si>
-  <si>
-    <t>0.9520,0.0022,0.0115,0.0078</t>
-  </si>
-  <si>
-    <t>0.8873,0.0038,0.1102,0.0044</t>
-  </si>
-  <si>
-    <t>0.9640,0.0087,0.0060,0.0033</t>
-  </si>
-  <si>
-    <t>0.9569,0.0033,0.0017,0.0117</t>
-  </si>
-  <si>
-    <t>0.9560,0.0091,0.0141,0.0047</t>
-  </si>
-  <si>
-    <t>0.9859,0.0013,0.0005,0.0034</t>
-  </si>
-  <si>
-    <t>0.9696,0.0021,0.0048,0.0097</t>
-  </si>
-  <si>
-    <t>0.9790,0.0008,0.0088,0.0007</t>
-  </si>
-  <si>
-    <t>0.9673,0.0009,0.0375,0.0003</t>
-  </si>
-  <si>
-    <t>0.9586,0.0010,0.0195,0.0030</t>
-  </si>
-  <si>
-    <t>0.9429,0.0018,0.0624,0.0010</t>
-  </si>
-  <si>
-    <t>0.9940,0.0001,0.0027,0.0001</t>
-  </si>
-  <si>
-    <t>0.0966,0.0038,0.9568,0.0009</t>
-  </si>
-  <si>
-    <t>0.2341,0.0325,0.6650,0.0388</t>
-  </si>
-  <si>
-    <t>0.8536,0.0016,0.3129,0.0001</t>
-  </si>
-  <si>
-    <t>0.6003,0.0012,0.7025,0.0001</t>
-  </si>
-  <si>
-    <t>0.8208,0.0024,0.2939,0.0010</t>
-  </si>
-  <si>
-    <t>0.7400,0.0017,0.0011,0.3687</t>
-  </si>
-  <si>
-    <t>0.9780,0.0024,0.0032,0.0061</t>
-  </si>
-  <si>
-    <t>0.8841,0.0121,0.0034,0.0328</t>
-  </si>
-  <si>
-    <t>0.8538,0.0254,0.0194,0.0446</t>
-  </si>
-  <si>
-    <t>0.9464,0.0024,0.0040,0.0325</t>
-  </si>
-  <si>
-    <t>0.9620,0.0008,0.0017,0.0222</t>
-  </si>
-  <si>
-    <t>0.9560,0.0014,0.0012,0.0428</t>
-  </si>
-  <si>
-    <t>0.6485,0.0136,0.0073,0.2499</t>
-  </si>
-  <si>
-    <t>0.1735,0.0114,0.8851,0.0050</t>
-  </si>
-  <si>
-    <t>0.9757,0.0006,0.0098,0.0016</t>
-  </si>
-  <si>
-    <t>0.9230,0.0038,0.0200,0.0156</t>
-  </si>
-  <si>
-    <t>0.8412,0.0023,0.2862,0.0005</t>
-  </si>
-  <si>
-    <t>0.2378,0.0208,0.8443,0.0015</t>
-  </si>
-  <si>
-    <t>0.8426,0.0017,0.2412,0.0009</t>
-  </si>
-  <si>
-    <t>0.0297,0.0026,0.9848,0.0002</t>
-  </si>
-  <si>
-    <t>0.9756,0.0003,0.0353,0.0001</t>
-  </si>
-  <si>
-    <t>0.0007,0.0010,0.9994,0.0000</t>
-  </si>
-  <si>
-    <t>0.4465,0.0011,0.8329,0.0001</t>
-  </si>
-  <si>
-    <t>0.9699,0.0008,0.0169,0.0011</t>
-  </si>
-  <si>
-    <t>0.9537,0.0019,0.0587,0.0007</t>
-  </si>
-  <si>
-    <t>0.9816,0.0003,0.0225,0.0002</t>
-  </si>
-  <si>
-    <t>0.9846,0.0006,0.0120,0.0002</t>
-  </si>
-  <si>
-    <t>0.8813,0.0100,0.0051,0.0520</t>
-  </si>
-  <si>
-    <t>0.9688,0.0023,0.0017,0.0116</t>
-  </si>
-  <si>
-    <t>0.9660,0.0023,0.0024,0.0139</t>
-  </si>
-  <si>
-    <t>0.9772,0.0012,0.0014,0.0106</t>
-  </si>
-  <si>
-    <t>0.9360,0.0029,0.0025,0.0570</t>
-  </si>
-  <si>
-    <t>0.9646,0.0016,0.0012,0.0313</t>
-  </si>
-  <si>
-    <t>0.9661,0.0023,0.0005,0.0171</t>
-  </si>
-  <si>
-    <t>0.9941,0.0002,0.0001,0.0027</t>
-  </si>
-  <si>
-    <t>0.7740,0.0096,0.3641,0.0008</t>
-  </si>
-  <si>
-    <t>0.0608,0.0171,0.9753,0.0002</t>
-  </si>
-  <si>
-    <t>0.7682,0.0221,0.3209,0.0008</t>
-  </si>
-  <si>
-    <t>0.9077,0.0037,0.1197,0.0005</t>
-  </si>
-  <si>
-    <t>0.5248,0.0147,0.6994,0.0006</t>
-  </si>
-  <si>
-    <t>0.9830,0.0004,0.0066,0.0010</t>
-  </si>
-  <si>
-    <t>0.7178,0.0127,0.4731,0.0014</t>
-  </si>
-  <si>
-    <t>0.0859,0.0012,0.9612,0.0005</t>
-  </si>
-  <si>
-    <t>0.9707,0.0008,0.0067,0.0055</t>
-  </si>
-  <si>
-    <t>0.9565,0.0004,0.0060,0.0115</t>
-  </si>
-  <si>
-    <t>0.9878,0.0000,0.0003,0.0061</t>
-  </si>
-  <si>
-    <t>0.7750,0.0001,0.0012,0.2971</t>
-  </si>
-  <si>
-    <t>0.6284,0.0002,0.0018,0.5401</t>
-  </si>
-  <si>
-    <t>0.9756,0.0006,0.0110,0.0014</t>
+    <t>0.9368,0.0066,0.0260,0.0138</t>
+  </si>
+  <si>
+    <t>0.0758,0.0015,0.0020,0.9676</t>
+  </si>
+  <si>
+    <t>0.7131,0.0022,0.0063,0.3467</t>
+  </si>
+  <si>
+    <t>0.5355,0.0076,0.0009,0.5739</t>
+  </si>
+  <si>
+    <t>0.9979,0.0006,0.0001,0.0005</t>
+  </si>
+  <si>
+    <t>0.9978,0.0009,0.0001,0.0004</t>
+  </si>
+  <si>
+    <t>0.9979,0.0004,0.0005,0.0002</t>
+  </si>
+  <si>
+    <t>0.9964,0.0012,0.0002,0.0009</t>
+  </si>
+  <si>
+    <t>0.9961,0.0031,0.0007,0.0003</t>
+  </si>
+  <si>
+    <t>0.9993,0.0005,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9981,0.0008,0.0004,0.0002</t>
+  </si>
+  <si>
+    <t>0.9983,0.0006,0.0004,0.0002</t>
+  </si>
+  <si>
+    <t>0.9913,0.0007,0.0055,0.0002</t>
+  </si>
+  <si>
+    <t>0.1188,0.0031,0.9458,0.0005</t>
+  </si>
+  <si>
+    <t>0.8400,0.0019,0.3704,0.0003</t>
+  </si>
+  <si>
+    <t>0.4504,0.0085,0.7100,0.0005</t>
+  </si>
+  <si>
+    <t>0.8256,0.0006,0.2059,0.0032</t>
+  </si>
+  <si>
+    <t>0.0016,0.9960,0.0013,0.0002</t>
+  </si>
+  <si>
+    <t>0.0015,0.9956,0.0038,0.0007</t>
+  </si>
+  <si>
+    <t>0.4988,0.7253,0.0017,0.0002</t>
+  </si>
+  <si>
+    <t>0.0040,0.9896,0.0051,0.0013</t>
+  </si>
+  <si>
+    <t>0.0003,0.9989,0.0006,0.0003</t>
+  </si>
+  <si>
+    <t>0.8814,0.0039,0.1215,0.0067</t>
+  </si>
+  <si>
+    <t>0.7965,0.0113,0.3022,0.0035</t>
+  </si>
+  <si>
+    <t>0.0005,0.0002,0.9987,0.0003</t>
+  </si>
+  <si>
+    <t>0.0182,0.0008,0.9788,0.0023</t>
+  </si>
+  <si>
+    <t>0.0918,0.0014,0.9555,0.0011</t>
+  </si>
+  <si>
+    <t>0.0094,0.0001,0.9956,0.0001</t>
+  </si>
+  <si>
+    <t>0.0026,0.0016,0.9949,0.0017</t>
+  </si>
+  <si>
+    <t>0.1787,0.7141,0.1511,0.0102</t>
+  </si>
+  <si>
+    <t>0.5562,0.1284,0.3296,0.0035</t>
+  </si>
+  <si>
+    <t>0.0048,0.0106,0.9932,0.0036</t>
+  </si>
+  <si>
+    <t>0.0183,0.4315,0.5152,0.0015</t>
+  </si>
+  <si>
+    <t>0.9047,0.0611,0.0268,0.0062</t>
+  </si>
+  <si>
+    <t>0.2488,0.0084,0.6849,0.0693</t>
+  </si>
+  <si>
+    <t>0.4267,0.7521,0.0023,0.0005</t>
+  </si>
+  <si>
+    <t>0.0148,0.9584,0.4992,0.0075</t>
+  </si>
+  <si>
+    <t>0.1095,0.4945,0.4302,0.0230</t>
+  </si>
+  <si>
+    <t>0.0217,0.0096,0.9767,0.0016</t>
+  </si>
+  <si>
+    <t>0.3203,0.0073,0.7612,0.0032</t>
+  </si>
+  <si>
+    <t>0.0033,0.0007,0.9734,0.0459</t>
+  </si>
+  <si>
+    <t>0.0096,0.0056,0.9875,0.0008</t>
+  </si>
+  <si>
+    <t>0.0010,0.9913,0.0201,0.0002</t>
+  </si>
+  <si>
+    <t>0.0050,0.0021,0.9905,0.0008</t>
+  </si>
+  <si>
+    <t>0.0148,0.4048,0.0016,0.8507</t>
+  </si>
+  <si>
+    <t>0.0085,0.9707,0.0199,0.0209</t>
+  </si>
+  <si>
+    <t>0.0125,0.9763,0.0433,0.0013</t>
+  </si>
+  <si>
+    <t>0.0006,0.9974,0.0572,0.0009</t>
+  </si>
+  <si>
+    <t>0.0026,0.1064,0.9836,0.0027</t>
+  </si>
+  <si>
+    <t>0.0016,0.0141,0.9975,0.0001</t>
+  </si>
+  <si>
+    <t>0.0079,0.0022,0.9863,0.0023</t>
+  </si>
+  <si>
+    <t>0.0807,0.0009,0.9498,0.0015</t>
+  </si>
+  <si>
+    <t>0.0061,0.0015,0.9940,0.0003</t>
+  </si>
+  <si>
+    <t>0.0056,0.1069,0.9869,0.0006</t>
+  </si>
+  <si>
+    <t>0.9876,0.0149,0.0006,0.0010</t>
+  </si>
+  <si>
+    <t>0.9958,0.0018,0.0006,0.0004</t>
+  </si>
+  <si>
+    <t>0.9907,0.0026,0.0024,0.0018</t>
+  </si>
+  <si>
+    <t>0.0062,0.0285,0.9928,0.0063</t>
+  </si>
+  <si>
+    <t>0.9943,0.0030,0.0016,0.0004</t>
+  </si>
+  <si>
+    <t>0.9942,0.0029,0.0009,0.0007</t>
+  </si>
+  <si>
+    <t>0.9848,0.0135,0.0023,0.0004</t>
+  </si>
+  <si>
+    <t>0.0020,0.9067,0.9652,0.0009</t>
+  </si>
+  <si>
+    <t>0.0234,0.0398,0.9848,0.0020</t>
+  </si>
+  <si>
+    <t>0.0030,0.0017,0.9948,0.0015</t>
+  </si>
+  <si>
+    <t>0.0008,0.9258,0.9784,0.0006</t>
+  </si>
+  <si>
+    <t>0.0014,0.0020,0.9959,0.0006</t>
+  </si>
+  <si>
+    <t>0.0035,0.9966,0.0008,0.0000</t>
+  </si>
+  <si>
+    <t>0.0075,0.9924,0.0006,0.0001</t>
+  </si>
+  <si>
+    <t>0.9869,0.0025,0.0040,0.0016</t>
+  </si>
+  <si>
+    <t>0.1662,0.0619,0.8623,0.0045</t>
+  </si>
+  <si>
+    <t>0.0016,0.0031,0.9967,0.0015</t>
+  </si>
+  <si>
+    <t>0.0002,0.9901,0.9733,0.0001</t>
+  </si>
+  <si>
+    <t>0.0032,0.9783,0.5730,0.0011</t>
+  </si>
+  <si>
+    <t>0.0002,0.9979,0.0044,0.0008</t>
+  </si>
+  <si>
+    <t>0.0018,0.9404,0.8468,0.0007</t>
+  </si>
+  <si>
+    <t>0.0050,0.0001,0.0032,0.9952</t>
+  </si>
+  <si>
+    <t>0.0013,0.0015,0.0005,0.9990</t>
+  </si>
+  <si>
+    <t>0.0099,0.0002,0.0000,0.9978</t>
+  </si>
+  <si>
+    <t>0.0080,0.0018,0.0010,0.9957</t>
+  </si>
+  <si>
+    <t>0.0049,0.0003,0.0002,0.9986</t>
+  </si>
+  <si>
+    <t>0.0171,0.0092,0.0015,0.9897</t>
+  </si>
+  <si>
+    <t>0.0002,0.9896,0.9902,0.0002</t>
+  </si>
+  <si>
+    <t>0.0011,0.1115,0.9983,0.0001</t>
+  </si>
+  <si>
+    <t>0.0104,0.7376,0.7376,0.0027</t>
+  </si>
+  <si>
+    <t>0.0023,0.1731,0.9809,0.0014</t>
+  </si>
+  <si>
+    <t>0.0033,0.9723,0.5066,0.0003</t>
+  </si>
+  <si>
+    <t>0.0015,0.9409,0.9588,0.0007</t>
+  </si>
+  <si>
+    <t>0.9972,0.0007,0.0003,0.0006</t>
+  </si>
+  <si>
+    <t>0.9920,0.0072,0.0009,0.0012</t>
+  </si>
+  <si>
+    <t>0.9961,0.0030,0.0003,0.0003</t>
+  </si>
+  <si>
+    <t>0.9988,0.0002,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9981,0.0012,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9995,0.0001,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9974,0.0007,0.0007,0.0002</t>
+  </si>
+  <si>
+    <t>0.9975,0.0026,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9984,0.0002,0.0001,0.0005</t>
+  </si>
+  <si>
+    <t>0.9960,0.0024,0.0004,0.0005</t>
+  </si>
+  <si>
+    <t>0.9958,0.0022,0.0009,0.0004</t>
+  </si>
+  <si>
+    <t>0.9986,0.0003,0.0000,0.0003</t>
+  </si>
+  <si>
+    <t>0.9977,0.0005,0.0003,0.0004</t>
+  </si>
+  <si>
+    <t>0.9948,0.0021,0.0004,0.0013</t>
+  </si>
+  <si>
+    <t>0.9996,0.0001,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.0152,0.0027,0.9875,0.0024</t>
+  </si>
+  <si>
+    <t>0.1781,0.0078,0.8904,0.0012</t>
+  </si>
+  <si>
+    <t>0.9800,0.0005,0.0124,0.0010</t>
+  </si>
+  <si>
+    <t>0.0194,0.0004,0.9814,0.0019</t>
+  </si>
+  <si>
+    <t>0.1078,0.9295,0.0011,0.0008</t>
+  </si>
+  <si>
+    <t>0.0012,0.9973,0.0005,0.0002</t>
+  </si>
+  <si>
+    <t>0.0899,0.9354,0.0016,0.0013</t>
+  </si>
+  <si>
+    <t>0.0058,0.9888,0.0011,0.0009</t>
+  </si>
+  <si>
+    <t>0.0267,0.9625,0.0081,0.0052</t>
+  </si>
+  <si>
+    <t>0.0122,0.9761,0.0060,0.0037</t>
+  </si>
+  <si>
+    <t>0.9574,0.0595,0.0023,0.0003</t>
+  </si>
+  <si>
+    <t>0.7312,0.0092,0.3876,0.0103</t>
+  </si>
+  <si>
+    <t>0.1686,0.0124,0.8827,0.0023</t>
+  </si>
+  <si>
+    <t>0.6499,0.0156,0.4528,0.0049</t>
+  </si>
+  <si>
+    <t>0.7833,0.0924,0.1212,0.0078</t>
+  </si>
+  <si>
+    <t>0.0333,0.0329,0.0257,0.9553</t>
+  </si>
+  <si>
+    <t>0.0122,0.9732,0.0123,0.0070</t>
+  </si>
+  <si>
+    <t>0.0178,0.9723,0.0101,0.0057</t>
+  </si>
+  <si>
+    <t>0.0036,0.9812,0.0153,0.0091</t>
+  </si>
+  <si>
+    <t>0.0013,0.9939,0.1192,0.0005</t>
+  </si>
+  <si>
+    <t>0.0042,0.9901,0.0035,0.0022</t>
+  </si>
+  <si>
+    <t>0.8138,0.1875,0.0235,0.0020</t>
+  </si>
+  <si>
+    <t>0.8910,0.1170,0.0139,0.0023</t>
+  </si>
+  <si>
+    <t>0.9972,0.0008,0.0003,0.0005</t>
+  </si>
+  <si>
+    <t>0.9978,0.0003,0.0003,0.0005</t>
+  </si>
+  <si>
+    <t>0.9981,0.0002,0.0004,0.0004</t>
+  </si>
+  <si>
+    <t>0.9924,0.0035,0.0024,0.0005</t>
+  </si>
+  <si>
+    <t>0.9987,0.0002,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.9824,0.0107,0.0058,0.0002</t>
+  </si>
+  <si>
+    <t>0.9977,0.0002,0.0003,0.0005</t>
+  </si>
+  <si>
+    <t>0.9862,0.0065,0.0051,0.0016</t>
+  </si>
+  <si>
+    <t>0.0002,0.9481,0.9963,0.0004</t>
+  </si>
+  <si>
+    <t>0.0004,0.8567,0.9946,0.0002</t>
+  </si>
+  <si>
+    <t>0.0030,0.0105,0.9895,0.0031</t>
+  </si>
+  <si>
+    <t>0.0486,0.0137,0.9553,0.0007</t>
+  </si>
+  <si>
+    <t>0.9863,0.0016,0.0070,0.0008</t>
+  </si>
+  <si>
+    <t>0.6369,0.1339,0.2283,0.0338</t>
+  </si>
+  <si>
+    <t>0.3051,0.0011,0.8496,0.0027</t>
+  </si>
+  <si>
+    <t>0.9578,0.0059,0.0172,0.0051</t>
+  </si>
+  <si>
+    <t>0.0320,0.0004,0.0004,0.9919</t>
+  </si>
+  <si>
+    <t>0.0003,0.0001,0.0007,0.9996</t>
+  </si>
+  <si>
+    <t>0.0145,0.0203,0.0004,0.9878</t>
+  </si>
+  <si>
+    <t>0.0032,0.0001,0.0013,0.9981</t>
+  </si>
+  <si>
+    <t>0.0026,0.9613,0.2690,0.0024</t>
+  </si>
+  <si>
+    <t>0.9976,0.0005,0.0006,0.0002</t>
+  </si>
+  <si>
+    <t>0.0110,0.9816,0.0034,0.0056</t>
+  </si>
+  <si>
+    <t>0.9944,0.0011,0.0004,0.0016</t>
+  </si>
+  <si>
+    <t>0.0998,0.8992,0.0143,0.0033</t>
+  </si>
+  <si>
+    <t>0.9838,0.0049,0.0078,0.0014</t>
+  </si>
+  <si>
+    <t>0.0740,0.0098,0.0251,0.9422</t>
+  </si>
+  <si>
+    <t>0.9953,0.0005,0.0012,0.0009</t>
+  </si>
+  <si>
+    <t>0.0388,0.0878,0.9421,0.0743</t>
+  </si>
+  <si>
+    <t>0.7853,0.0031,0.0043,0.2592</t>
+  </si>
+  <si>
+    <t>0.9626,0.0071,0.0043,0.0198</t>
+  </si>
+  <si>
+    <t>0.5788,0.3987,0.0226,0.0098</t>
+  </si>
+  <si>
+    <t>0.9883,0.0039,0.0015,0.0016</t>
+  </si>
+  <si>
+    <t>0.8857,0.0781,0.0368,0.0040</t>
+  </si>
+  <si>
+    <t>0.1443,0.7754,0.0866,0.0068</t>
+  </si>
+  <si>
+    <t>0.7700,0.2153,0.0262,0.0026</t>
+  </si>
+  <si>
+    <t>0.9921,0.0018,0.0032,0.0003</t>
+  </si>
+  <si>
+    <t>0.9961,0.0006,0.0010,0.0005</t>
+  </si>
+  <si>
+    <t>0.9942,0.0020,0.0018,0.0009</t>
+  </si>
+  <si>
+    <t>0.9955,0.0005,0.0004,0.0014</t>
+  </si>
+  <si>
+    <t>0.9952,0.0005,0.0014,0.0007</t>
+  </si>
+  <si>
+    <t>0.9962,0.0003,0.0003,0.0013</t>
+  </si>
+  <si>
+    <t>0.9821,0.0140,0.0046,0.0009</t>
+  </si>
+  <si>
+    <t>0.9967,0.0001,0.0008,0.0005</t>
+  </si>
+  <si>
+    <t>0.9975,0.0002,0.0003,0.0007</t>
+  </si>
+  <si>
+    <t>0.9148,0.0816,0.0009,0.0062</t>
+  </si>
+  <si>
+    <t>0.7318,0.4130,0.0039,0.0006</t>
+  </si>
+  <si>
+    <t>0.8364,0.2175,0.0075,0.0038</t>
+  </si>
+  <si>
+    <t>0.8917,0.0347,0.1114,0.0064</t>
+  </si>
+  <si>
+    <t>0.9955,0.0070,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9883,0.0044,0.0033,0.0010</t>
+  </si>
+  <si>
+    <t>0.9892,0.0126,0.0010,0.0004</t>
+  </si>
+  <si>
+    <t>0.8818,0.1848,0.0007,0.0016</t>
+  </si>
+  <si>
+    <t>0.0030,0.0357,0.9954,0.0041</t>
+  </si>
+  <si>
+    <t>0.9898,0.0025,0.0023,0.0018</t>
+  </si>
+  <si>
+    <t>0.0041,0.0040,0.9960,0.0004</t>
+  </si>
+  <si>
+    <t>0.0009,0.0125,0.9963,0.0031</t>
+  </si>
+  <si>
+    <t>0.0318,0.0011,0.9853,0.0007</t>
+  </si>
+  <si>
+    <t>0.0368,0.1361,0.9464,0.0025</t>
+  </si>
+  <si>
+    <t>0.0016,0.0028,0.9969,0.0003</t>
+  </si>
+  <si>
+    <t>0.0023,0.0007,0.9973,0.0009</t>
+  </si>
+  <si>
+    <t>0.0022,0.0023,0.9913,0.0029</t>
+  </si>
+  <si>
+    <t>0.0509,0.0076,0.9332,0.0139</t>
+  </si>
+  <si>
+    <t>0.1885,0.0307,0.8408,0.0097</t>
+  </si>
+  <si>
+    <t>0.8912,0.0266,0.0695,0.0058</t>
+  </si>
+  <si>
+    <t>0.1629,0.5671,0.2824,0.0137</t>
+  </si>
+  <si>
+    <t>0.2573,0.1376,0.6735,0.0042</t>
+  </si>
+  <si>
+    <t>0.2241,0.2657,0.5003,0.0017</t>
+  </si>
+  <si>
+    <t>0.8034,0.0076,0.2869,0.0085</t>
+  </si>
+  <si>
+    <t>0.1043,0.0105,0.9137,0.0105</t>
+  </si>
+  <si>
+    <t>0.7369,0.4313,0.0032,0.0004</t>
+  </si>
+  <si>
+    <t>0.8809,0.1867,0.0007,0.0026</t>
+  </si>
+  <si>
+    <t>0.9420,0.1075,0.0013,0.0006</t>
+  </si>
+  <si>
+    <t>0.9843,0.0367,0.0003,0.0002</t>
+  </si>
+  <si>
+    <t>0.9947,0.0134,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.6666,0.0761,0.3003,0.0078</t>
+  </si>
+  <si>
+    <t>0.9894,0.0003,0.0065,0.0005</t>
+  </si>
+  <si>
+    <t>0.9203,0.0072,0.0231,0.0192</t>
+  </si>
+  <si>
+    <t>0.7766,0.0027,0.3798,0.0019</t>
+  </si>
+  <si>
+    <t>0.9114,0.0030,0.1302,0.0026</t>
+  </si>
+  <si>
+    <t>0.0150,0.0034,0.9821,0.0092</t>
+  </si>
+  <si>
+    <t>0.0132,0.1786,0.9562,0.0099</t>
+  </si>
+  <si>
+    <t>0.0043,0.0123,0.9932,0.0010</t>
+  </si>
+  <si>
+    <t>0.1047,0.0192,0.8801,0.0015</t>
+  </si>
+  <si>
+    <t>0.0018,0.0045,0.9850,0.0083</t>
+  </si>
+  <si>
+    <t>0.9960,0.0021,0.0006,0.0003</t>
+  </si>
+  <si>
+    <t>0.9965,0.0011,0.0003,0.0006</t>
+  </si>
+  <si>
+    <t>0.9979,0.0012,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.9975,0.0020,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.9864,0.0175,0.0005,0.0006</t>
+  </si>
+  <si>
+    <t>0.9918,0.0081,0.0008,0.0005</t>
+  </si>
+  <si>
+    <t>0.9784,0.0082,0.0002,0.0037</t>
+  </si>
+  <si>
+    <t>0.9979,0.0007,0.0002,0.0003</t>
+  </si>
+  <si>
+    <t>0.0468,0.0194,0.9563,0.0066</t>
+  </si>
+  <si>
+    <t>0.0240,0.0402,0.9200,0.0262</t>
+  </si>
+  <si>
+    <t>0.8836,0.0147,0.0617,0.0229</t>
+  </si>
+  <si>
+    <t>0.0225,0.0019,0.9875,0.0003</t>
+  </si>
+  <si>
+    <t>0.0009,0.0018,0.9949,0.0028</t>
+  </si>
+  <si>
+    <t>0.0347,0.0278,0.9527,0.0016</t>
+  </si>
+  <si>
+    <t>0.0104,0.0020,0.9935,0.0005</t>
+  </si>
+  <si>
+    <t>0.0107,0.0036,0.9801,0.0019</t>
+  </si>
+  <si>
+    <t>0.0012,0.0022,0.9942,0.0072</t>
+  </si>
+  <si>
+    <t>0.0033,0.0024,0.9914,0.0013</t>
+  </si>
+  <si>
+    <t>0.0318,0.0112,0.9501,0.0023</t>
+  </si>
+  <si>
+    <t>0.8843,0.0021,0.2397,0.0016</t>
+  </si>
+  <si>
+    <t>0.4694,0.0001,0.7349,0.0002</t>
+  </si>
+  <si>
+    <t>0.9224,0.0033,0.0903,0.0036</t>
+  </si>
+  <si>
+    <t>0.9956,0.0056,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.9974,0.0015,0.0003,0.0002</t>
+  </si>
+  <si>
+    <t>0.9987,0.0004,0.0004,0.0002</t>
+  </si>
+  <si>
+    <t>0.9875,0.0043,0.0064,0.0003</t>
+  </si>
+  <si>
+    <t>0.9989,0.0002,0.0000,0.0002</t>
+  </si>
+  <si>
+    <t>0.9973,0.0028,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9959,0.0028,0.0009,0.0002</t>
+  </si>
+  <si>
+    <t>0.9990,0.0002,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.0218,0.0036,0.9752,0.0009</t>
+  </si>
+  <si>
+    <t>0.0023,0.0157,0.9888,0.0008</t>
+  </si>
+  <si>
+    <t>0.0018,0.0208,0.9955,0.0008</t>
+  </si>
+  <si>
+    <t>0.0764,0.0087,0.9129,0.0018</t>
+  </si>
+  <si>
+    <t>0.0008,0.0006,0.9988,0.0001</t>
+  </si>
+  <si>
+    <t>0.3912,0.0024,0.3163,0.0551</t>
+  </si>
+  <si>
+    <t>0.0678,0.0034,0.9652,0.0008</t>
+  </si>
+  <si>
+    <t>0.0173,0.0028,0.8792,0.0561</t>
+  </si>
+  <si>
+    <t>0.9359,0.0067,0.0069,0.0405</t>
+  </si>
+  <si>
+    <t>0.0148,0.0193,0.0011,0.9895</t>
+  </si>
+  <si>
+    <t>0.3205,0.0003,0.0003,0.8961</t>
+  </si>
+  <si>
+    <t>0.0026,0.0002,0.0005,0.9988</t>
+  </si>
+  <si>
+    <t>0.0023,0.0002,0.0007,0.9985</t>
+  </si>
+  <si>
+    <t>0.9536,0.0030,0.0043,0.0240</t>
   </si>
 </sst>
 </file>
@@ -1967,7 +1964,7 @@
         <v>260</v>
       </c>
       <c r="C3" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D3" t="s">
         <v>265</v>
@@ -1995,7 +1992,7 @@
         <v>260</v>
       </c>
       <c r="C5" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D5" t="s">
         <v>267</v>
@@ -2135,7 +2132,7 @@
         <v>261</v>
       </c>
       <c r="C15" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D15" t="s">
         <v>277</v>
@@ -2163,7 +2160,7 @@
         <v>261</v>
       </c>
       <c r="C17" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D17" t="s">
         <v>279</v>
@@ -2191,7 +2188,7 @@
         <v>262</v>
       </c>
       <c r="C19" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D19" t="s">
         <v>281</v>
@@ -2205,7 +2202,7 @@
         <v>262</v>
       </c>
       <c r="C20" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D20" t="s">
         <v>282</v>
@@ -2219,7 +2216,7 @@
         <v>262</v>
       </c>
       <c r="C21" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D21" t="s">
         <v>283</v>
@@ -2233,7 +2230,7 @@
         <v>262</v>
       </c>
       <c r="C22" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D22" t="s">
         <v>284</v>
@@ -2247,7 +2244,7 @@
         <v>262</v>
       </c>
       <c r="C23" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D23" t="s">
         <v>285</v>
@@ -2303,7 +2300,7 @@
         <v>261</v>
       </c>
       <c r="C27" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D27" t="s">
         <v>289</v>
@@ -2317,7 +2314,7 @@
         <v>261</v>
       </c>
       <c r="C28" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D28" t="s">
         <v>290</v>
@@ -2359,7 +2356,7 @@
         <v>259</v>
       </c>
       <c r="C31" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D31" t="s">
         <v>293</v>
@@ -2401,7 +2398,7 @@
         <v>263</v>
       </c>
       <c r="C34" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D34" t="s">
         <v>296</v>
@@ -2429,7 +2426,7 @@
         <v>259</v>
       </c>
       <c r="C36" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D36" t="s">
         <v>298</v>
@@ -2443,7 +2440,7 @@
         <v>259</v>
       </c>
       <c r="C37" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D37" t="s">
         <v>299</v>
@@ -2457,7 +2454,7 @@
         <v>262</v>
       </c>
       <c r="C38" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D38" t="s">
         <v>300</v>
@@ -2471,7 +2468,7 @@
         <v>263</v>
       </c>
       <c r="C39" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D39" t="s">
         <v>301</v>
@@ -2485,7 +2482,7 @@
         <v>261</v>
       </c>
       <c r="C40" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D40" t="s">
         <v>302</v>
@@ -2499,7 +2496,7 @@
         <v>261</v>
       </c>
       <c r="C41" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D41" t="s">
         <v>303</v>
@@ -2513,7 +2510,7 @@
         <v>261</v>
       </c>
       <c r="C42" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D42" t="s">
         <v>304</v>
@@ -2555,7 +2552,7 @@
         <v>261</v>
       </c>
       <c r="C45" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D45" t="s">
         <v>307</v>
@@ -2569,7 +2566,7 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D46" t="s">
         <v>308</v>
@@ -2583,7 +2580,7 @@
         <v>262</v>
       </c>
       <c r="C47" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D47" t="s">
         <v>309</v>
@@ -2597,7 +2594,7 @@
         <v>262</v>
       </c>
       <c r="C48" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D48" t="s">
         <v>310</v>
@@ -2611,7 +2608,7 @@
         <v>262</v>
       </c>
       <c r="C49" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D49" t="s">
         <v>311</v>
@@ -2849,7 +2846,7 @@
         <v>263</v>
       </c>
       <c r="C66" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D66" t="s">
         <v>328</v>
@@ -2877,7 +2874,7 @@
         <v>262</v>
       </c>
       <c r="C68" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D68" t="s">
         <v>330</v>
@@ -2919,7 +2916,7 @@
         <v>261</v>
       </c>
       <c r="C71" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D71" t="s">
         <v>333</v>
@@ -2947,7 +2944,7 @@
         <v>263</v>
       </c>
       <c r="C73" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D73" t="s">
         <v>335</v>
@@ -2961,7 +2958,7 @@
         <v>263</v>
       </c>
       <c r="C74" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D74" t="s">
         <v>336</v>
@@ -3003,7 +3000,7 @@
         <v>260</v>
       </c>
       <c r="C77" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D77" t="s">
         <v>339</v>
@@ -3017,7 +3014,7 @@
         <v>260</v>
       </c>
       <c r="C78" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D78" t="s">
         <v>340</v>
@@ -3045,7 +3042,7 @@
         <v>260</v>
       </c>
       <c r="C80" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D80" t="s">
         <v>342</v>
@@ -3059,7 +3056,7 @@
         <v>260</v>
       </c>
       <c r="C81" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D81" t="s">
         <v>343</v>
@@ -3073,7 +3070,7 @@
         <v>260</v>
       </c>
       <c r="C82" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D82" t="s">
         <v>344</v>
@@ -3087,7 +3084,7 @@
         <v>263</v>
       </c>
       <c r="C83" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D83" t="s">
         <v>345</v>
@@ -3115,7 +3112,7 @@
         <v>263</v>
       </c>
       <c r="C85" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D85" t="s">
         <v>347</v>
@@ -3143,7 +3140,7 @@
         <v>263</v>
       </c>
       <c r="C87" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D87" t="s">
         <v>349</v>
@@ -3157,7 +3154,7 @@
         <v>262</v>
       </c>
       <c r="C88" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D88" t="s">
         <v>350</v>
@@ -3314,7 +3311,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>361</v>
+        <v>356</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3328,7 +3325,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3342,7 +3339,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3356,7 +3353,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3370,7 +3367,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3384,7 +3381,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3398,7 +3395,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3412,7 +3409,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3426,7 +3423,7 @@
         <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3437,10 +3434,10 @@
         <v>261</v>
       </c>
       <c r="C108" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3451,10 +3448,10 @@
         <v>262</v>
       </c>
       <c r="C109" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3465,10 +3462,10 @@
         <v>262</v>
       </c>
       <c r="C110" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3479,10 +3476,10 @@
         <v>262</v>
       </c>
       <c r="C111" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3493,10 +3490,10 @@
         <v>262</v>
       </c>
       <c r="C112" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3507,10 +3504,10 @@
         <v>262</v>
       </c>
       <c r="C113" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3524,7 +3521,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3538,7 +3535,7 @@
         <v>259</v>
       </c>
       <c r="D115" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3552,7 +3549,7 @@
         <v>259</v>
       </c>
       <c r="D116" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3563,10 +3560,10 @@
         <v>261</v>
       </c>
       <c r="C117" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D117" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3580,7 +3577,7 @@
         <v>259</v>
       </c>
       <c r="D118" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3594,7 +3591,7 @@
         <v>259</v>
       </c>
       <c r="D119" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3605,10 +3602,10 @@
         <v>262</v>
       </c>
       <c r="C120" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D120" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3619,10 +3616,10 @@
         <v>262</v>
       </c>
       <c r="C121" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3633,10 +3630,10 @@
         <v>262</v>
       </c>
       <c r="C122" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3647,10 +3644,10 @@
         <v>262</v>
       </c>
       <c r="C123" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3661,10 +3658,10 @@
         <v>263</v>
       </c>
       <c r="C124" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D124" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3675,10 +3672,10 @@
         <v>262</v>
       </c>
       <c r="C125" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3692,7 +3689,7 @@
         <v>259</v>
       </c>
       <c r="D126" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3706,7 +3703,7 @@
         <v>259</v>
       </c>
       <c r="D127" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3720,7 +3717,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3734,7 +3731,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3748,7 +3745,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3762,7 +3759,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3776,7 +3773,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3790,7 +3787,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3804,7 +3801,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3818,7 +3815,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3829,10 +3826,10 @@
         <v>263</v>
       </c>
       <c r="C136" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D136" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3843,10 +3840,10 @@
         <v>261</v>
       </c>
       <c r="C137" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D137" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3860,7 +3857,7 @@
         <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3874,7 +3871,7 @@
         <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3888,7 +3885,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3902,7 +3899,7 @@
         <v>259</v>
       </c>
       <c r="D141" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3913,10 +3910,10 @@
         <v>261</v>
       </c>
       <c r="C142" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D142" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3930,7 +3927,7 @@
         <v>259</v>
       </c>
       <c r="D143" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3941,10 +3938,10 @@
         <v>260</v>
       </c>
       <c r="C144" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3958,7 +3955,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3972,7 +3969,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3983,10 +3980,10 @@
         <v>260</v>
       </c>
       <c r="C147" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -3997,10 +3994,10 @@
         <v>263</v>
       </c>
       <c r="C148" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D148" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -4014,7 +4011,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -4025,10 +4022,10 @@
         <v>262</v>
       </c>
       <c r="C150" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D150" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -4042,7 +4039,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4053,10 +4050,10 @@
         <v>262</v>
       </c>
       <c r="C152" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D152" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4070,7 +4067,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4081,10 +4078,10 @@
         <v>259</v>
       </c>
       <c r="C154" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D154" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4098,7 +4095,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4112,7 +4109,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4126,7 +4123,7 @@
         <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4140,7 +4137,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4154,7 +4151,7 @@
         <v>259</v>
       </c>
       <c r="D159" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4168,7 +4165,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4182,7 +4179,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4193,10 +4190,10 @@
         <v>262</v>
       </c>
       <c r="C162" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D162" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4210,7 +4207,7 @@
         <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4224,7 +4221,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4238,7 +4235,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4252,7 +4249,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4266,7 +4263,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4280,7 +4277,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4294,7 +4291,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4308,7 +4305,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4322,7 +4319,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4336,7 +4333,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4350,7 +4347,7 @@
         <v>259</v>
       </c>
       <c r="D173" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4364,7 +4361,7 @@
         <v>259</v>
       </c>
       <c r="D174" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4378,7 +4375,7 @@
         <v>259</v>
       </c>
       <c r="D175" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4392,7 +4389,7 @@
         <v>259</v>
       </c>
       <c r="D176" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4406,7 +4403,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4420,7 +4417,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4434,7 +4431,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4448,7 +4445,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4462,7 +4459,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4476,7 +4473,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4490,7 +4487,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4504,7 +4501,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4515,10 +4512,10 @@
         <v>261</v>
       </c>
       <c r="C185" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4532,7 +4529,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4546,7 +4543,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4560,7 +4557,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4574,7 +4571,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4585,10 +4582,10 @@
         <v>259</v>
       </c>
       <c r="C190" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4599,10 +4596,10 @@
         <v>259</v>
       </c>
       <c r="C191" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4616,7 +4613,7 @@
         <v>259</v>
       </c>
       <c r="D192" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4627,10 +4624,10 @@
         <v>261</v>
       </c>
       <c r="C193" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D193" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4641,10 +4638,10 @@
         <v>261</v>
       </c>
       <c r="C194" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D194" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4655,10 +4652,10 @@
         <v>261</v>
       </c>
       <c r="C195" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D195" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4672,7 +4669,7 @@
         <v>259</v>
       </c>
       <c r="D196" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4683,10 +4680,10 @@
         <v>259</v>
       </c>
       <c r="C197" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D197" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4700,7 +4697,7 @@
         <v>259</v>
       </c>
       <c r="D198" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4714,7 +4711,7 @@
         <v>259</v>
       </c>
       <c r="D199" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4728,7 +4725,7 @@
         <v>259</v>
       </c>
       <c r="D200" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4742,7 +4739,7 @@
         <v>259</v>
       </c>
       <c r="D201" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4756,7 +4753,7 @@
         <v>259</v>
       </c>
       <c r="D202" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4770,7 +4767,7 @@
         <v>259</v>
       </c>
       <c r="D203" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4784,7 +4781,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4798,7 +4795,7 @@
         <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4812,7 +4809,7 @@
         <v>259</v>
       </c>
       <c r="D206" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4826,7 +4823,7 @@
         <v>259</v>
       </c>
       <c r="D207" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4840,7 +4837,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4854,7 +4851,7 @@
         <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4865,10 +4862,10 @@
         <v>261</v>
       </c>
       <c r="C210" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4882,7 +4879,7 @@
         <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4893,10 +4890,10 @@
         <v>261</v>
       </c>
       <c r="C212" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D212" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4910,7 +4907,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4924,7 +4921,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4938,7 +4935,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4952,7 +4949,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4966,7 +4963,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4980,7 +4977,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4994,7 +4991,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -5008,7 +5005,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -5022,7 +5019,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -5033,10 +5030,10 @@
         <v>259</v>
       </c>
       <c r="C222" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D222" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -5050,7 +5047,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5061,10 +5058,10 @@
         <v>261</v>
       </c>
       <c r="C224" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5078,7 +5075,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5089,10 +5086,10 @@
         <v>261</v>
       </c>
       <c r="C226" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5106,7 +5103,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5117,10 +5114,10 @@
         <v>261</v>
       </c>
       <c r="C228" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5134,7 +5131,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5148,7 +5145,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5159,10 +5156,10 @@
         <v>261</v>
       </c>
       <c r="C231" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5176,7 +5173,7 @@
         <v>259</v>
       </c>
       <c r="D232" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5187,10 +5184,10 @@
         <v>259</v>
       </c>
       <c r="C233" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D233" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5204,7 +5201,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5218,7 +5215,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5232,7 +5229,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5246,7 +5243,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5260,7 +5257,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5274,7 +5271,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5288,7 +5285,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5302,7 +5299,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5316,7 +5313,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5327,10 +5324,10 @@
         <v>261</v>
       </c>
       <c r="C243" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5344,7 +5341,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5355,10 +5352,10 @@
         <v>261</v>
       </c>
       <c r="C245" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5369,10 +5366,10 @@
         <v>261</v>
       </c>
       <c r="C246" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5386,7 +5383,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5400,7 +5397,7 @@
         <v>259</v>
       </c>
       <c r="D248" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5411,10 +5408,10 @@
         <v>261</v>
       </c>
       <c r="C249" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5428,7 +5425,7 @@
         <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5442,7 +5439,7 @@
         <v>259</v>
       </c>
       <c r="D251" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5453,10 +5450,10 @@
         <v>260</v>
       </c>
       <c r="C252" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5467,10 +5464,10 @@
         <v>260</v>
       </c>
       <c r="C253" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5481,10 +5478,10 @@
         <v>260</v>
       </c>
       <c r="C254" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5498,7 +5495,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5512,7 +5509,7 @@
         <v>259</v>
       </c>
       <c r="D256" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
     </row>
   </sheetData>
